--- a/research/traditional_assets/database/data/canada/canada_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_beverage_soft.xlsx
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>1.561</v>
+        <v>0.667</v>
       </c>
       <c r="G2">
-        <v>-0.8140832750174948</v>
+        <v>-0.7490949566119499</v>
       </c>
       <c r="H2">
-        <v>-0.818002099370189</v>
+        <v>-0.7516993202718913</v>
       </c>
       <c r="I2">
-        <v>-1.187893631910427</v>
+        <v>-0.8987756248851811</v>
       </c>
       <c r="J2">
-        <v>-1.187893631910427</v>
+        <v>-0.8987756248851811</v>
       </c>
       <c r="K2">
-        <v>-92.78</v>
+        <v>-85.27</v>
       </c>
       <c r="L2">
-        <v>-1.623163051084675</v>
+        <v>-0.9214692501377828</v>
       </c>
       <c r="M2">
-        <v>0.008</v>
+        <v>5.736000000000001</v>
       </c>
       <c r="N2">
-        <v>1.36986301369863e-05</v>
+        <v>0.0588006150691953</v>
       </c>
       <c r="O2">
-        <v>-8.622547962923044e-05</v>
+        <v>-0.06726867597044682</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +627,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.008</v>
+        <v>5.736000000000001</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>113.501</v>
+        <v>42.36</v>
       </c>
       <c r="V2">
-        <v>0.1943510273972603</v>
+        <v>0.4342388518708355</v>
       </c>
       <c r="W2">
-        <v>-1.045731707317073</v>
+        <v>-0.5609022556390977</v>
       </c>
       <c r="X2">
-        <v>0.04931906355424946</v>
+        <v>0.09668428396005554</v>
       </c>
       <c r="Y2">
-        <v>-1.095050770871323</v>
+        <v>-0.6575865395991533</v>
       </c>
       <c r="Z2">
-        <v>2.176114516313245</v>
+        <v>0.9463022047695012</v>
       </c>
       <c r="AA2">
-        <v>-0.7937935686979986</v>
+        <v>-0.9210526315789473</v>
       </c>
       <c r="AB2">
-        <v>0.04766812903622004</v>
+        <v>0.08575901575345851</v>
       </c>
       <c r="AC2">
-        <v>-0.8415212613279792</v>
+        <v>-1.008690659241797</v>
       </c>
       <c r="AD2">
-        <v>48.635</v>
+        <v>83.30200000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>48.635</v>
+        <v>83.30200000000001</v>
       </c>
       <c r="AG2">
-        <v>-64.86600000000001</v>
+        <v>40.94200000000001</v>
       </c>
       <c r="AH2">
-        <v>0.0768768721300592</v>
+        <v>0.4606086744962732</v>
       </c>
       <c r="AI2">
-        <v>0.2030561760223785</v>
+        <v>0.4698576359903436</v>
       </c>
       <c r="AJ2">
-        <v>-0.1249503981630947</v>
+        <v>0.295627184241689</v>
       </c>
       <c r="AK2">
-        <v>-0.51475232910629</v>
+        <v>0.3034269113331159</v>
       </c>
       <c r="AL2">
-        <v>5.192</v>
+        <v>8.69</v>
       </c>
       <c r="AM2">
-        <v>5.154</v>
+        <v>8.250999999999999</v>
       </c>
       <c r="AN2">
-        <v>-0.7434270865178844</v>
+        <v>-1.069482603671845</v>
       </c>
       <c r="AO2">
-        <v>-13.07781201848998</v>
+        <v>-9.570771001150749</v>
       </c>
       <c r="AP2">
-        <v>0.9915316416997861</v>
+        <v>-0.525638721273591</v>
       </c>
       <c r="AQ2">
-        <v>-13.17423360496702</v>
+        <v>-10.07999030420555</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CENTR Brands Corp. (CNSX:CNTR)</t>
+          <t>Flow Beverage Corp. (TSX:FLOW)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,31 +719,31 @@
         </is>
       </c>
       <c r="G3">
-        <v>-4.032258064516129</v>
+        <v>-1.090379008746356</v>
       </c>
       <c r="H3">
-        <v>-4.032258064516129</v>
+        <v>-1.090379008746356</v>
       </c>
       <c r="I3">
-        <v>-4.193548387096774</v>
+        <v>-0.9183673469387756</v>
       </c>
       <c r="J3">
-        <v>-4.193548387096774</v>
+        <v>-0.9183673469387756</v>
       </c>
       <c r="K3">
-        <v>-16.5</v>
+        <v>-37.3</v>
       </c>
       <c r="L3">
-        <v>-10.64516129032258</v>
+        <v>-1.087463556851312</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>5.65</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.7271557271557273</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0.1514745308310992</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -755,70 +755,79 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>5.65</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>3.13</v>
+        <v>18.1</v>
       </c>
       <c r="V3">
-        <v>0.05378006872852233</v>
+        <v>2.32947232947233</v>
       </c>
       <c r="W3">
-        <v>47.82608695652174</v>
+        <v>-0.5609022556390977</v>
       </c>
       <c r="X3">
-        <v>0.04775452603611711</v>
+        <v>0.2408968730997241</v>
       </c>
       <c r="Y3">
-        <v>47.77833243048563</v>
+        <v>-0.8017991287388218</v>
       </c>
       <c r="Z3">
-        <v>-8.072916666666668</v>
+        <v>0.6191335740072201</v>
       </c>
       <c r="AA3">
-        <v>33.85416666666667</v>
+        <v>-0.5685920577617328</v>
       </c>
       <c r="AB3">
-        <v>0.04773817785782802</v>
+        <v>0.1134214522088573</v>
       </c>
       <c r="AC3">
-        <v>33.80642848880884</v>
+        <v>-0.6820135099705902</v>
       </c>
       <c r="AD3">
-        <v>0.035</v>
+        <v>34.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.035</v>
+        <v>34.1</v>
       </c>
       <c r="AG3">
-        <v>-3.095</v>
+        <v>16</v>
       </c>
       <c r="AH3">
-        <v>0.0006010131364299821</v>
+        <v>0.8144256030570813</v>
       </c>
       <c r="AI3">
-        <v>-0.01639344262295082</v>
+        <v>0.4934876989869755</v>
       </c>
       <c r="AJ3">
-        <v>-0.05616550222302875</v>
+        <v>0.6731173748422381</v>
       </c>
       <c r="AK3">
-        <v>0.5878442545109211</v>
+        <v>0.3137254901960784</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AN3">
-        <v>-0.005384615384615385</v>
+        <v>-1.144295302013423</v>
+      </c>
+      <c r="AO3">
+        <v>-8.75</v>
       </c>
       <c r="AP3">
-        <v>0.4761538461538461</v>
+        <v>-0.5369127516778524</v>
+      </c>
+      <c r="AQ3">
+        <v>-8.75</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BevCanna Enterprises Inc. (CNSX:BEV)</t>
+          <t>The Tinley Beverage Company Inc. (OTCPK:TNYB.F)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -837,23 +846,26 @@
           <t>Beverage (Soft)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.667</v>
+      </c>
       <c r="G4">
-        <v>-2.982089552238806</v>
+        <v>-8.225997045790251</v>
       </c>
       <c r="H4">
-        <v>-2.985074626865672</v>
+        <v>-8.581979320531756</v>
       </c>
       <c r="I4">
-        <v>-5.024875621890548</v>
+        <v>-7.843426883308714</v>
       </c>
       <c r="J4">
-        <v>-5.024875621890548</v>
+        <v>-7.843426883308714</v>
       </c>
       <c r="K4">
-        <v>-15.6</v>
+        <v>-5.56</v>
       </c>
       <c r="L4">
-        <v>-7.761194029850747</v>
+        <v>-8.212703101920235</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -877,73 +889,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.519</v>
+        <v>0.197</v>
       </c>
       <c r="V4">
-        <v>0.01827464788732394</v>
+        <v>0.02487373737373737</v>
       </c>
       <c r="W4">
-        <v>-0.8524590163934426</v>
+        <v>-1.039252336448598</v>
       </c>
       <c r="X4">
-        <v>0.04969143651211607</v>
+        <v>0.09668428396005554</v>
       </c>
       <c r="Y4">
-        <v>-0.9021504529055586</v>
+        <v>-1.135936620408654</v>
       </c>
       <c r="Z4">
-        <v>0.1308423382372087</v>
+        <v>0.1094053005817712</v>
       </c>
       <c r="AA4">
-        <v>-0.6574664757193073</v>
+        <v>-0.8581124757595345</v>
       </c>
       <c r="AB4">
-        <v>0.04766812903622004</v>
+        <v>0.08437732388429786</v>
       </c>
       <c r="AC4">
-        <v>-0.7051346047555274</v>
+        <v>-0.9424897996438324</v>
       </c>
       <c r="AD4">
-        <v>2.31</v>
+        <v>2.42</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2.31</v>
+        <v>2.42</v>
       </c>
       <c r="AG4">
-        <v>1.791</v>
+        <v>2.223</v>
       </c>
       <c r="AH4">
-        <v>0.07521979811136438</v>
+        <v>0.2340425531914894</v>
       </c>
       <c r="AI4">
-        <v>0.03811252268602541</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="AJ4">
-        <v>0.05932231459706535</v>
+        <v>0.2191659272404614</v>
       </c>
       <c r="AK4">
-        <v>0.02980479605931005</v>
+        <v>0.4571252313386798</v>
       </c>
       <c r="AL4">
-        <v>0.513</v>
+        <v>0.247</v>
       </c>
       <c r="AM4">
-        <v>0.513</v>
+        <v>0.246</v>
       </c>
       <c r="AN4">
-        <v>-0.282051282051282</v>
+        <v>-0.5330396475770925</v>
       </c>
       <c r="AO4">
-        <v>-19.68810916179337</v>
+        <v>-21.49797570850202</v>
       </c>
       <c r="AP4">
-        <v>-0.2186813186813187</v>
+        <v>-0.489647577092511</v>
       </c>
       <c r="AQ4">
-        <v>-19.68810916179337</v>
+        <v>-21.58536585365853</v>
       </c>
     </row>
     <row r="5">
@@ -954,7 +966,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GURU Organic Energy Corp. (TSX:GURU )</t>
+          <t>Wildpack Beverage Inc. (TSXV:CANS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,31 +975,31 @@
         </is>
       </c>
       <c r="G5">
-        <v>0.03242152466367713</v>
+        <v>-0.3993808049535604</v>
       </c>
       <c r="H5">
-        <v>0.03242152466367713</v>
+        <v>-0.3993808049535604</v>
       </c>
       <c r="I5">
-        <v>-0.1582959641255605</v>
+        <v>-0.758513931888545</v>
       </c>
       <c r="J5">
-        <v>-0.1582959641255605</v>
+        <v>-0.758513931888545</v>
       </c>
       <c r="K5">
-        <v>-5.62</v>
+        <v>-25.1</v>
       </c>
       <c r="L5">
-        <v>-0.2520179372197309</v>
+        <v>-0.7770897832817338</v>
       </c>
       <c r="M5">
-        <v>0.008</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>1.948368241597662e-05</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>-0.001423487544483986</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -999,79 +1011,76 @@
         <v>0</v>
       </c>
       <c r="S5">
-        <v>0.008</v>
-      </c>
-      <c r="T5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>54.9</v>
+        <v>0.513</v>
       </c>
       <c r="V5">
-        <v>0.1337067705796395</v>
+        <v>0.07820121951219512</v>
       </c>
       <c r="W5">
-        <v>-2.432900432900433</v>
+        <v>-3.118012422360248</v>
       </c>
       <c r="X5">
-        <v>0.04783358332579309</v>
+        <v>0.3265583533533064</v>
       </c>
       <c r="Y5">
-        <v>-2.480734016226226</v>
+        <v>-3.444570775713555</v>
       </c>
       <c r="Z5">
-        <v>5.014616595457612</v>
+        <v>1.214285714285714</v>
       </c>
       <c r="AA5">
-        <v>-0.7937935686979986</v>
+        <v>-0.9210526315789473</v>
       </c>
       <c r="AB5">
-        <v>0.04772769262998063</v>
+        <v>0.08763802766284999</v>
       </c>
       <c r="AC5">
-        <v>-0.8415212613279792</v>
+        <v>-1.008690659241797</v>
       </c>
       <c r="AD5">
-        <v>1.6</v>
+        <v>44.7</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.6</v>
+        <v>44.7</v>
       </c>
       <c r="AG5">
-        <v>-53.3</v>
+        <v>44.187</v>
       </c>
       <c r="AH5">
-        <v>0.003881610868510432</v>
+        <v>0.872024970737417</v>
       </c>
       <c r="AI5">
-        <v>0.0248062015503876</v>
+        <v>0.8461101646791596</v>
       </c>
       <c r="AJ5">
-        <v>-0.1491743632801567</v>
+        <v>0.8707312747551579</v>
       </c>
       <c r="AK5">
-        <v>-5.552083333333332</v>
+        <v>0.8446011812603933</v>
       </c>
       <c r="AL5">
-        <v>0.063</v>
+        <v>4.79</v>
       </c>
       <c r="AM5">
-        <v>0.025</v>
+        <v>4.79</v>
       </c>
       <c r="AN5">
-        <v>-0.4494382022471911</v>
+        <v>-2.031818181818182</v>
       </c>
       <c r="AO5">
-        <v>-56.03174603174603</v>
+        <v>-5.11482254697286</v>
       </c>
       <c r="AP5">
-        <v>14.97191011235955</v>
+        <v>-2.0085</v>
       </c>
       <c r="AQ5">
-        <v>-141.2</v>
+        <v>-5.11482254697286</v>
       </c>
     </row>
     <row r="6">
@@ -1082,7 +1091,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Tinley Beverage Company Inc. (OTCPK:TNYB.F)</t>
+          <t>GURU Organic Energy Corp. (TSX:GURU )</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1090,35 +1099,32 @@
           <t>Beverage (Soft)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>1.561</v>
-      </c>
       <c r="G6">
-        <v>-8.020000000000001</v>
+        <v>-0.3370833333333333</v>
       </c>
       <c r="H6">
-        <v>-8.383333333333335</v>
+        <v>-0.3370833333333333</v>
       </c>
       <c r="I6">
-        <v>-11.11666666666667</v>
+        <v>-0.6625</v>
       </c>
       <c r="J6">
-        <v>-11.11666666666667</v>
+        <v>-0.6625</v>
       </c>
       <c r="K6">
-        <v>-6.86</v>
+        <v>-15.4</v>
       </c>
       <c r="L6">
-        <v>-11.43333333333333</v>
+        <v>-0.6416666666666667</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>0.018</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.0003345724907063197</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>-0.001168831168831169</v>
       </c>
       <c r="P6">
         <v>-0</v>
@@ -1130,76 +1136,79 @@
         <v>0</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>0.018</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
       </c>
       <c r="U6">
-        <v>0.452</v>
+        <v>21.2</v>
       </c>
       <c r="V6">
-        <v>0.02306122448979592</v>
+        <v>0.3940520446096654</v>
       </c>
       <c r="W6">
-        <v>-1.045731707317073</v>
+        <v>-0.2448330683624801</v>
       </c>
       <c r="X6">
-        <v>0.04931906355424946</v>
+        <v>0.08696237939676879</v>
       </c>
       <c r="Y6">
-        <v>-1.095050770871323</v>
+        <v>-0.331795447759249</v>
       </c>
       <c r="Z6">
-        <v>0.09022556390977446</v>
+        <v>2.5</v>
       </c>
       <c r="AA6">
-        <v>-1.003007518796993</v>
+        <v>-1.65625</v>
       </c>
       <c r="AB6">
-        <v>0.04754273103864811</v>
+        <v>0.08561814020469351</v>
       </c>
       <c r="AC6">
-        <v>-1.050550249835641</v>
+        <v>-1.741868140204693</v>
       </c>
       <c r="AD6">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="AG6">
-        <v>0.8380000000000001</v>
+        <v>-19.57</v>
       </c>
       <c r="AH6">
-        <v>0.0617520344662518</v>
+        <v>0.02940645859642792</v>
       </c>
       <c r="AI6">
-        <v>0.1942771084337349</v>
+        <v>0.03407902989755383</v>
       </c>
       <c r="AJ6">
-        <v>0.04100205499559643</v>
+        <v>-0.5717207128250074</v>
       </c>
       <c r="AK6">
-        <v>0.1354234001292825</v>
+        <v>-0.734885467517837</v>
       </c>
       <c r="AL6">
-        <v>0.146</v>
+        <v>0.053</v>
       </c>
       <c r="AM6">
-        <v>0.146</v>
+        <v>-0.385</v>
       </c>
       <c r="AN6">
-        <v>-0.2197614991482112</v>
+        <v>-0.1044871794871795</v>
       </c>
       <c r="AO6">
-        <v>-45.68493150684932</v>
+        <v>-300</v>
       </c>
       <c r="AP6">
-        <v>-0.1427597955706985</v>
+        <v>1.254487179487179</v>
       </c>
       <c r="AQ6">
-        <v>-45.68493150684932</v>
+        <v>41.2987012987013</v>
       </c>
     </row>
     <row r="7">
@@ -1210,7 +1219,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Flow Beverage Corp. (TSX:FLOW)</t>
+          <t>CENTR Brands Corp. (CNSX:CNTR)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1219,31 +1228,31 @@
         </is>
       </c>
       <c r="G7">
-        <v>-0.9837133550488599</v>
+        <v>-4.253968253968254</v>
       </c>
       <c r="H7">
-        <v>-0.9837133550488599</v>
+        <v>-4.253968253968254</v>
       </c>
       <c r="I7">
-        <v>-1.338762214983714</v>
+        <v>-4.73015873015873</v>
       </c>
       <c r="J7">
-        <v>-1.338762214983714</v>
+        <v>-4.73015873015873</v>
       </c>
       <c r="K7">
-        <v>-48.2</v>
+        <v>-1.91</v>
       </c>
       <c r="L7">
-        <v>-1.570032573289902</v>
+        <v>-1.515873015873016</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>0.068</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.003162790697674419</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>-0.0356020942408377</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1255,61 +1264,64 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>0.068</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
       </c>
       <c r="U7">
-        <v>54.5</v>
+        <v>2.35</v>
       </c>
       <c r="V7">
-        <v>0.8110119047619048</v>
+        <v>0.1093023255813954</v>
+      </c>
+      <c r="W7">
+        <v>0.880184331797235</v>
       </c>
       <c r="X7">
-        <v>0.06323394566367686</v>
+        <v>0.08663482389860098</v>
+      </c>
+      <c r="Y7">
+        <v>0.793549507898634</v>
       </c>
       <c r="AB7">
-        <v>0.0473646485489251</v>
+        <v>0.08575901575345851</v>
       </c>
       <c r="AD7">
-        <v>43.4</v>
+        <v>0.452</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>43.4</v>
+        <v>0.452</v>
       </c>
       <c r="AG7">
-        <v>-11.1</v>
+        <v>-1.898</v>
       </c>
       <c r="AH7">
-        <v>0.3924050632911392</v>
+        <v>0.02059037900874635</v>
       </c>
       <c r="AI7">
-        <v>0.3949044585987261</v>
+        <v>0.1828478964401295</v>
       </c>
       <c r="AJ7">
-        <v>-0.1978609625668449</v>
+        <v>-0.09682685440261199</v>
       </c>
       <c r="AK7">
-        <v>-0.200361010830325</v>
+        <v>-15.55737704918034</v>
       </c>
       <c r="AL7">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="AN7">
-        <v>-1.050847457627119</v>
-      </c>
-      <c r="AO7">
-        <v>-9.194630872483222</v>
+        <v>-0.07596638655462185</v>
       </c>
       <c r="AP7">
-        <v>0.2687651331719129</v>
-      </c>
-      <c r="AQ7">
-        <v>-9.194630872483222</v>
+        <v>0.3189915966386555</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/canada/canada_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_beverage_soft.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.667</v>
+        <v>1.382</v>
       </c>
       <c r="G2">
-        <v>-0.7490949566119499</v>
+        <v>-0.6383826590182243</v>
       </c>
       <c r="H2">
-        <v>-0.7516993202718913</v>
+        <v>-0.6391187369917254</v>
       </c>
       <c r="I2">
-        <v>-0.8987756248851811</v>
+        <v>-0.6207590909860061</v>
       </c>
       <c r="J2">
-        <v>-0.8987756248851811</v>
+        <v>-0.6207590909860061</v>
       </c>
       <c r="K2">
-        <v>-85.27</v>
+        <v>-99.34</v>
       </c>
       <c r="L2">
-        <v>-0.9214692501377828</v>
+        <v>-0.8404825964092932</v>
       </c>
       <c r="M2">
-        <v>5.736000000000001</v>
+        <v>1.485</v>
       </c>
       <c r="N2">
-        <v>0.0588006150691953</v>
+        <v>0.0210161335975092</v>
       </c>
       <c r="O2">
-        <v>-0.06726867597044682</v>
+        <v>-0.01494866116368029</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +627,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>5.736000000000001</v>
+        <v>1.485</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>42.36</v>
+        <v>37.67899999999999</v>
       </c>
       <c r="V2">
-        <v>0.4342388518708355</v>
+        <v>0.53324370223606</v>
       </c>
       <c r="W2">
-        <v>-0.5609022556390977</v>
+        <v>-1.556818181818182</v>
       </c>
       <c r="X2">
-        <v>0.09668428396005554</v>
+        <v>0.08159786531953676</v>
       </c>
       <c r="Y2">
-        <v>-0.6575865395991533</v>
+        <v>-1.638416047137719</v>
       </c>
       <c r="Z2">
-        <v>0.9463022047695012</v>
+        <v>0.9377201612135444</v>
       </c>
       <c r="AA2">
-        <v>-0.9210526315789473</v>
+        <v>-0.7526218383713756</v>
       </c>
       <c r="AB2">
-        <v>0.08575901575345851</v>
+        <v>0.06781007204597447</v>
       </c>
       <c r="AC2">
-        <v>-1.008690659241797</v>
+        <v>-0.8189061243319977</v>
       </c>
       <c r="AD2">
-        <v>83.30200000000001</v>
+        <v>92.36999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>83.30200000000001</v>
+        <v>92.36999999999999</v>
       </c>
       <c r="AG2">
-        <v>40.94200000000001</v>
+        <v>54.691</v>
       </c>
       <c r="AH2">
-        <v>0.4606086744962732</v>
+        <v>0.5665828375145679</v>
       </c>
       <c r="AI2">
-        <v>0.4698576359903436</v>
+        <v>0.7799346465934326</v>
       </c>
       <c r="AJ2">
-        <v>0.295627184241689</v>
+        <v>0.4363028615647262</v>
       </c>
       <c r="AK2">
-        <v>0.3034269113331159</v>
+        <v>0.6772543774921367</v>
       </c>
       <c r="AL2">
-        <v>8.69</v>
+        <v>12.538</v>
       </c>
       <c r="AM2">
-        <v>8.250999999999999</v>
+        <v>11.225</v>
       </c>
       <c r="AN2">
-        <v>-1.069482603671845</v>
+        <v>-1.355392516507704</v>
       </c>
       <c r="AO2">
-        <v>-9.570771001150749</v>
+        <v>-5.851810496091881</v>
       </c>
       <c r="AP2">
-        <v>-0.525638721273591</v>
+        <v>-0.8025091709464417</v>
       </c>
       <c r="AQ2">
-        <v>-10.07999030420555</v>
+        <v>-6.53630289532294</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Flow Beverage Corp. (TSX:FLOW)</t>
+          <t>GURU Organic Energy Corp. (TSX:GURU )</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,31 +719,31 @@
         </is>
       </c>
       <c r="G3">
-        <v>-1.090379008746356</v>
+        <v>-0.6157407407407407</v>
       </c>
       <c r="H3">
-        <v>-1.090379008746356</v>
+        <v>-0.6157407407407407</v>
       </c>
       <c r="I3">
-        <v>-0.9183673469387756</v>
+        <v>-0.4861111111111111</v>
       </c>
       <c r="J3">
-        <v>-0.9183673469387756</v>
+        <v>-0.4861111111111111</v>
       </c>
       <c r="K3">
-        <v>-37.3</v>
+        <v>-9.23</v>
       </c>
       <c r="L3">
-        <v>-1.087463556851312</v>
+        <v>-0.4273148148148148</v>
       </c>
       <c r="M3">
-        <v>5.65</v>
+        <v>1.39</v>
       </c>
       <c r="N3">
-        <v>0.7271557271557273</v>
+        <v>0.02938689217758985</v>
       </c>
       <c r="O3">
-        <v>-0.1514745308310992</v>
+        <v>-0.1505958829902492</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -755,79 +755,79 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>5.65</v>
+        <v>1.39</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
       <c r="U3">
-        <v>18.1</v>
+        <v>29.4</v>
       </c>
       <c r="V3">
-        <v>2.32947232947233</v>
+        <v>0.6215644820295984</v>
       </c>
       <c r="W3">
-        <v>-0.5609022556390977</v>
+        <v>-0.1997835497835498</v>
       </c>
       <c r="X3">
-        <v>0.2408968730997241</v>
+        <v>0.06958794987923814</v>
       </c>
       <c r="Y3">
-        <v>-0.8017991287388218</v>
+        <v>-0.2693714996627879</v>
       </c>
       <c r="Z3">
-        <v>0.6191335740072201</v>
+        <v>0.8111152835148328</v>
       </c>
       <c r="AA3">
-        <v>-0.5685920577617328</v>
+        <v>-0.3942921517085992</v>
       </c>
       <c r="AB3">
-        <v>0.1134214522088573</v>
+        <v>0.06879097176796961</v>
       </c>
       <c r="AC3">
-        <v>-0.6820135099705902</v>
+        <v>-0.4630831234765688</v>
       </c>
       <c r="AD3">
-        <v>34.1</v>
+        <v>1.28</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>34.1</v>
+        <v>1.28</v>
       </c>
       <c r="AG3">
-        <v>16</v>
+        <v>-28.12</v>
       </c>
       <c r="AH3">
-        <v>0.8144256030570813</v>
+        <v>0.02634829147797448</v>
       </c>
       <c r="AI3">
-        <v>0.4934876989869755</v>
+        <v>0.03528114663726571</v>
       </c>
       <c r="AJ3">
-        <v>0.6731173748422381</v>
+        <v>-1.466110531803962</v>
       </c>
       <c r="AK3">
-        <v>0.3137254901960784</v>
+        <v>-4.087209302325579</v>
       </c>
       <c r="AL3">
-        <v>3.6</v>
+        <v>0.048</v>
       </c>
       <c r="AM3">
-        <v>3.6</v>
+        <v>-1.262</v>
       </c>
       <c r="AN3">
-        <v>-1.144295302013423</v>
+        <v>-0.1267326732673267</v>
       </c>
       <c r="AO3">
-        <v>-8.75</v>
+        <v>-218.75</v>
       </c>
       <c r="AP3">
-        <v>-0.5369127516778524</v>
+        <v>2.784158415841584</v>
       </c>
       <c r="AQ3">
-        <v>-8.75</v>
+        <v>8.32012678288431</v>
       </c>
     </row>
     <row r="4">
@@ -838,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Tinley Beverage Company Inc. (OTCPK:TNYB.F)</t>
+          <t>Wildpack Beverage Inc. (TSXV:CANS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -846,26 +846,23 @@
           <t>Beverage (Soft)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.667</v>
-      </c>
       <c r="G4">
-        <v>-8.225997045790251</v>
+        <v>-0.3422562141491396</v>
       </c>
       <c r="H4">
-        <v>-8.581979320531756</v>
+        <v>-0.3422562141491396</v>
       </c>
       <c r="I4">
-        <v>-7.843426883308714</v>
+        <v>-0.3632887189292543</v>
       </c>
       <c r="J4">
-        <v>-7.843426883308714</v>
+        <v>-0.3632887189292543</v>
       </c>
       <c r="K4">
-        <v>-5.56</v>
+        <v>-35.4</v>
       </c>
       <c r="L4">
-        <v>-8.212703101920235</v>
+        <v>-0.6768642447418738</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -889,73 +886,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.197</v>
+        <v>1.08</v>
       </c>
       <c r="V4">
-        <v>0.02487373737373737</v>
+        <v>0.2589928057553957</v>
       </c>
       <c r="W4">
-        <v>-1.039252336448598</v>
+        <v>-4.354243542435424</v>
       </c>
       <c r="X4">
-        <v>0.09668428396005554</v>
+        <v>0.3924934689538861</v>
       </c>
       <c r="Y4">
-        <v>-1.135936620408654</v>
+        <v>-4.74673701138931</v>
       </c>
       <c r="Z4">
-        <v>0.1094053005817712</v>
+        <v>1.300445085411642</v>
       </c>
       <c r="AA4">
-        <v>-0.8581124757595345</v>
+        <v>-0.47243702911704</v>
       </c>
       <c r="AB4">
-        <v>0.08437732388429786</v>
+        <v>0.07667943194609368</v>
       </c>
       <c r="AC4">
-        <v>-0.9424897996438324</v>
+        <v>-0.5491164610631337</v>
       </c>
       <c r="AD4">
-        <v>2.42</v>
+        <v>60.8</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2.42</v>
+        <v>60.8</v>
       </c>
       <c r="AG4">
-        <v>2.223</v>
+        <v>59.72</v>
       </c>
       <c r="AH4">
-        <v>0.2340425531914894</v>
+        <v>0.9358165307064799</v>
       </c>
       <c r="AI4">
-        <v>0.4782608695652174</v>
+        <v>1.330415754923414</v>
       </c>
       <c r="AJ4">
-        <v>0.2191659272404614</v>
+        <v>0.9347315698857411</v>
       </c>
       <c r="AK4">
-        <v>0.4571252313386798</v>
+        <v>1.338413267593008</v>
       </c>
       <c r="AL4">
-        <v>0.247</v>
+        <v>7.51</v>
       </c>
       <c r="AM4">
-        <v>0.246</v>
+        <v>7.51</v>
       </c>
       <c r="AN4">
-        <v>-0.5330396475770925</v>
+        <v>-3.597633136094675</v>
       </c>
       <c r="AO4">
-        <v>-21.49797570850202</v>
+        <v>-2.529960053262317</v>
       </c>
       <c r="AP4">
-        <v>-0.489647577092511</v>
+        <v>-3.533727810650888</v>
       </c>
       <c r="AQ4">
-        <v>-21.58536585365853</v>
+        <v>-2.529960053262317</v>
       </c>
     </row>
     <row r="5">
@@ -966,7 +963,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wildpack Beverage Inc. (TSXV:CANS)</t>
+          <t>Flow Beverage Corp. (TSX:FLOW)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -975,22 +972,22 @@
         </is>
       </c>
       <c r="G5">
-        <v>-0.3993808049535604</v>
+        <v>-0.6812339331619538</v>
       </c>
       <c r="H5">
-        <v>-0.3993808049535604</v>
+        <v>-0.6812339331619538</v>
       </c>
       <c r="I5">
-        <v>-0.758513931888545</v>
+        <v>-0.7223650385604113</v>
       </c>
       <c r="J5">
-        <v>-0.758513931888545</v>
+        <v>-0.7223650385604113</v>
       </c>
       <c r="K5">
-        <v>-25.1</v>
+        <v>-33.4</v>
       </c>
       <c r="L5">
-        <v>-0.7770897832817338</v>
+        <v>-0.8586118251928021</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1014,73 +1011,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.513</v>
+        <v>5.76</v>
       </c>
       <c r="V5">
-        <v>0.07820121951219512</v>
+        <v>0.6981818181818181</v>
       </c>
       <c r="W5">
-        <v>-3.118012422360248</v>
+        <v>-0.9542857142857143</v>
       </c>
       <c r="X5">
-        <v>0.3265583533533064</v>
+        <v>0.1292308273289169</v>
       </c>
       <c r="Y5">
-        <v>-3.444570775713555</v>
+        <v>-1.083516541614631</v>
       </c>
       <c r="Z5">
-        <v>1.214285714285714</v>
+        <v>0.7423664122137404</v>
       </c>
       <c r="AA5">
-        <v>-0.9210526315789473</v>
+        <v>-0.5362595419847329</v>
       </c>
       <c r="AB5">
-        <v>0.08763802766284999</v>
+        <v>0.1013391166546024</v>
       </c>
       <c r="AC5">
-        <v>-1.008690659241797</v>
+        <v>-0.6375986586393354</v>
       </c>
       <c r="AD5">
-        <v>44.7</v>
+        <v>22.4</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>44.7</v>
+        <v>22.4</v>
       </c>
       <c r="AG5">
-        <v>44.187</v>
+        <v>16.64</v>
       </c>
       <c r="AH5">
-        <v>0.872024970737417</v>
+        <v>0.730831973898858</v>
       </c>
       <c r="AI5">
-        <v>0.8461101646791596</v>
+        <v>0.827790096082779</v>
       </c>
       <c r="AJ5">
-        <v>0.8707312747551579</v>
+        <v>0.6685415829650462</v>
       </c>
       <c r="AK5">
-        <v>0.8446011812603933</v>
+        <v>0.7812206572769953</v>
       </c>
       <c r="AL5">
-        <v>4.79</v>
+        <v>3.56</v>
       </c>
       <c r="AM5">
-        <v>4.79</v>
+        <v>3.56</v>
       </c>
       <c r="AN5">
-        <v>-2.031818181818182</v>
+        <v>-0.8175182481751825</v>
       </c>
       <c r="AO5">
-        <v>-5.11482254697286</v>
+        <v>-7.893258426966292</v>
       </c>
       <c r="AP5">
-        <v>-2.0085</v>
+        <v>-0.6072992700729928</v>
       </c>
       <c r="AQ5">
-        <v>-5.11482254697286</v>
+        <v>-7.893258426966292</v>
       </c>
     </row>
     <row r="6">
@@ -1091,7 +1088,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GURU Organic Energy Corp. (TSX:GURU )</t>
+          <t>The Tinley Beverage Company Inc. (OTCPK:TNYB.F)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1099,32 +1096,35 @@
           <t>Beverage (Soft)</t>
         </is>
       </c>
+      <c r="D6">
+        <v>1.382</v>
+      </c>
       <c r="G6">
-        <v>-0.3370833333333333</v>
+        <v>-2.150515463917526</v>
       </c>
       <c r="H6">
-        <v>-0.3370833333333333</v>
+        <v>-2.190721649484536</v>
       </c>
       <c r="I6">
-        <v>-0.6625</v>
+        <v>-1.88659793814433</v>
       </c>
       <c r="J6">
-        <v>-0.6625</v>
+        <v>-1.88659793814433</v>
       </c>
       <c r="K6">
-        <v>-15.4</v>
+        <v>-4.11</v>
       </c>
       <c r="L6">
-        <v>-0.6416666666666667</v>
+        <v>-2.118556701030928</v>
       </c>
       <c r="M6">
-        <v>0.018</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.0003345724907063197</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>-0.001168831168831169</v>
+        <v>0</v>
       </c>
       <c r="P6">
         <v>-0</v>
@@ -1136,79 +1136,76 @@
         <v>0</v>
       </c>
       <c r="S6">
-        <v>0.018</v>
-      </c>
-      <c r="T6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>21.2</v>
+        <v>0.043</v>
       </c>
       <c r="V6">
-        <v>0.3940520446096654</v>
+        <v>0.01031175059952038</v>
       </c>
       <c r="W6">
-        <v>-0.2448330683624801</v>
+        <v>-1.556818181818182</v>
       </c>
       <c r="X6">
-        <v>0.08696237939676879</v>
+        <v>0.08159786531953676</v>
       </c>
       <c r="Y6">
-        <v>-0.331795447759249</v>
+        <v>-1.638416047137719</v>
       </c>
       <c r="Z6">
-        <v>2.5</v>
+        <v>0.3989307012132428</v>
       </c>
       <c r="AA6">
-        <v>-1.65625</v>
+        <v>-0.7526218383713756</v>
       </c>
       <c r="AB6">
-        <v>0.08561814020469351</v>
+        <v>0.06628428596062207</v>
       </c>
       <c r="AC6">
-        <v>-1.741868140204693</v>
+        <v>-0.8189061243319977</v>
       </c>
       <c r="AD6">
-        <v>1.63</v>
+        <v>2.37</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.63</v>
+        <v>2.37</v>
       </c>
       <c r="AG6">
-        <v>-19.57</v>
+        <v>2.327</v>
       </c>
       <c r="AH6">
-        <v>0.02940645859642792</v>
+        <v>0.3623853211009174</v>
       </c>
       <c r="AI6">
-        <v>0.03407902989755383</v>
+        <v>1.975</v>
       </c>
       <c r="AJ6">
-        <v>-0.5717207128250074</v>
+        <v>0.3581653070647992</v>
       </c>
       <c r="AK6">
-        <v>-0.734885467517837</v>
+        <v>2.01123595505618</v>
       </c>
       <c r="AL6">
-        <v>0.053</v>
+        <v>0.879</v>
       </c>
       <c r="AM6">
-        <v>-0.385</v>
+        <v>0.876</v>
       </c>
       <c r="AN6">
-        <v>-0.1044871794871795</v>
+        <v>-0.9115384615384615</v>
       </c>
       <c r="AO6">
-        <v>-300</v>
+        <v>-4.163822525597269</v>
       </c>
       <c r="AP6">
-        <v>1.254487179487179</v>
+        <v>-0.8949999999999999</v>
       </c>
       <c r="AQ6">
-        <v>41.2987012987013</v>
+        <v>-4.178082191780822</v>
       </c>
     </row>
     <row r="7">
@@ -1219,7 +1216,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CENTR Brands Corp. (CNSX:CNTR)</t>
+          <t>HYTN Innovations Inc. (CNSX:HYTN)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1228,31 +1225,31 @@
         </is>
       </c>
       <c r="G7">
-        <v>-4.253968253968254</v>
+        <v>-3.686131386861314</v>
       </c>
       <c r="H7">
-        <v>-4.253968253968254</v>
+        <v>-3.686131386861314</v>
       </c>
       <c r="I7">
-        <v>-4.73015873015873</v>
+        <v>-3.248175182481752</v>
       </c>
       <c r="J7">
-        <v>-4.73015873015873</v>
+        <v>-3.248175182481752</v>
       </c>
       <c r="K7">
         <v>-1.91</v>
       </c>
       <c r="L7">
-        <v>-1.515873015873016</v>
+        <v>-3.485401459854014</v>
       </c>
       <c r="M7">
-        <v>0.068</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.003162790697674419</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>-0.0356020942408377</v>
+        <v>0</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1264,64 +1261,308 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>0.068</v>
-      </c>
-      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0.06</v>
+      </c>
+      <c r="V7">
+        <v>0.01680672268907563</v>
+      </c>
+      <c r="W7">
+        <v>-0.8162393162393162</v>
+      </c>
+      <c r="X7">
+        <v>0.07328835170623307</v>
+      </c>
+      <c r="Y7">
+        <v>-0.8895276679455493</v>
+      </c>
+      <c r="Z7">
+        <v>0.3024282560706402</v>
+      </c>
+      <c r="AA7">
+        <v>-0.9823399558498896</v>
+      </c>
+      <c r="AB7">
+        <v>0.06777634736538059</v>
+      </c>
+      <c r="AC7">
+        <v>-1.05011630321527</v>
+      </c>
+      <c r="AD7">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="AG7">
+        <v>0.6319999999999999</v>
+      </c>
+      <c r="AH7">
+        <v>0.1623650868137025</v>
+      </c>
+      <c r="AI7">
+        <v>0.7170984455958549</v>
+      </c>
+      <c r="AJ7">
+        <v>0.1504045692527368</v>
+      </c>
+      <c r="AK7">
+        <v>0.698342541436464</v>
+      </c>
+      <c r="AL7">
+        <v>0.114</v>
+      </c>
+      <c r="AM7">
+        <v>0.114</v>
+      </c>
+      <c r="AN7">
+        <v>-0.497841726618705</v>
+      </c>
+      <c r="AO7">
+        <v>-15.6140350877193</v>
+      </c>
+      <c r="AP7">
+        <v>-0.4546762589928057</v>
+      </c>
+      <c r="AQ7">
+        <v>-15.6140350877193</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CENTR Brands Corp. (CNSX:CNTR)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Beverage (Soft)</t>
+        </is>
+      </c>
+      <c r="G8">
+        <v>-9.046391752577319</v>
+      </c>
+      <c r="H8">
+        <v>-9.046391752577319</v>
+      </c>
+      <c r="I8">
+        <v>-8.556701030927835</v>
+      </c>
+      <c r="J8">
+        <v>-8.556701030927835</v>
+      </c>
+      <c r="K8">
+        <v>-4.99</v>
+      </c>
+      <c r="L8">
+        <v>-6.430412371134021</v>
+      </c>
+      <c r="M8">
+        <v>0.095</v>
+      </c>
+      <c r="N8">
+        <v>0.05428571428571428</v>
+      </c>
+      <c r="O8">
+        <v>-0.01903807615230461</v>
+      </c>
+      <c r="P8">
+        <v>-0</v>
+      </c>
+      <c r="Q8">
+        <v>-0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0.095</v>
+      </c>
+      <c r="T8">
         <v>1</v>
       </c>
-      <c r="U7">
-        <v>2.35</v>
-      </c>
-      <c r="V7">
-        <v>0.1093023255813954</v>
-      </c>
-      <c r="W7">
-        <v>0.880184331797235</v>
-      </c>
-      <c r="X7">
-        <v>0.08663482389860098</v>
-      </c>
-      <c r="Y7">
-        <v>0.793549507898634</v>
-      </c>
-      <c r="AB7">
-        <v>0.08575901575345851</v>
-      </c>
-      <c r="AD7">
-        <v>0.452</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0.452</v>
-      </c>
-      <c r="AG7">
-        <v>-1.898</v>
-      </c>
-      <c r="AH7">
-        <v>0.02059037900874635</v>
-      </c>
-      <c r="AI7">
-        <v>0.1828478964401295</v>
-      </c>
-      <c r="AJ7">
-        <v>-0.09682685440261199</v>
-      </c>
-      <c r="AK7">
-        <v>-15.55737704918034</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>-0.07596638655462185</v>
-      </c>
-      <c r="AP7">
-        <v>0.3189915966386555</v>
+      <c r="U8">
+        <v>1.22</v>
+      </c>
+      <c r="V8">
+        <v>0.6971428571428572</v>
+      </c>
+      <c r="W8">
+        <v>-2.47029702970297</v>
+      </c>
+      <c r="X8">
+        <v>0.07314615073801997</v>
+      </c>
+      <c r="Y8">
+        <v>-2.54344318044099</v>
+      </c>
+      <c r="Z8">
+        <v>6.360655737704924</v>
+      </c>
+      <c r="AA8">
+        <v>-54.42622950819677</v>
+      </c>
+      <c r="AB8">
+        <v>0.06781007204597447</v>
+      </c>
+      <c r="AC8">
+        <v>-54.49403958024274</v>
+      </c>
+      <c r="AD8">
+        <v>0.328</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0.328</v>
+      </c>
+      <c r="AG8">
+        <v>-0.8919999999999999</v>
+      </c>
+      <c r="AH8">
+        <v>0.1578440808469682</v>
+      </c>
+      <c r="AI8">
+        <v>0.2296918767507003</v>
+      </c>
+      <c r="AJ8">
+        <v>-1.03962703962704</v>
+      </c>
+      <c r="AK8">
+        <v>-4.288461538461534</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>-0.04932330827067669</v>
+      </c>
+      <c r="AP8">
+        <v>0.1341353383458646</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BevCanna Enterprises Inc. (CNSX:BEV)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Beverage (Soft)</t>
+        </is>
+      </c>
+      <c r="G9">
+        <v>-2.131924882629108</v>
+      </c>
+      <c r="H9">
+        <v>-2.136150234741784</v>
+      </c>
+      <c r="I9">
+        <v>-1.732394366197183</v>
+      </c>
+      <c r="J9">
+        <v>-1.732394366197183</v>
+      </c>
+      <c r="K9">
+        <v>-10.3</v>
+      </c>
+      <c r="L9">
+        <v>-4.83568075117371</v>
+      </c>
+      <c r="M9">
+        <v>-0</v>
+      </c>
+      <c r="N9">
+        <v>-0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>-0</v>
+      </c>
+      <c r="Q9">
+        <v>-0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0.116</v>
+      </c>
+      <c r="V9">
+        <v>0.08</v>
+      </c>
+      <c r="X9">
+        <v>0.1378462882518888</v>
+      </c>
+      <c r="AB9">
+        <v>0.06334583999415777</v>
+      </c>
+      <c r="AD9">
+        <v>4.5</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>4.5</v>
+      </c>
+      <c r="AG9">
+        <v>4.384</v>
+      </c>
+      <c r="AH9">
+        <v>0.7563025210084033</v>
+      </c>
+      <c r="AI9">
+        <v>0.7758620689655172</v>
+      </c>
+      <c r="AJ9">
+        <v>0.7514569763455605</v>
+      </c>
+      <c r="AK9">
+        <v>0.7712878254750176</v>
+      </c>
+      <c r="AL9">
+        <v>0.427</v>
+      </c>
+      <c r="AM9">
+        <v>0.427</v>
+      </c>
+      <c r="AN9">
+        <v>-1.446945337620579</v>
+      </c>
+      <c r="AO9">
+        <v>-8.641686182669789</v>
+      </c>
+      <c r="AP9">
+        <v>-1.409646302250804</v>
+      </c>
+      <c r="AQ9">
+        <v>-8.641686182669789</v>
       </c>
     </row>
   </sheetData>
